--- a/ml_model/training/data/disease_data/heart_disease_dataset.xlsx
+++ b/ml_model/training/data/disease_data/heart_disease_dataset.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Medi_Link\ml_model\training\data\disease_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF029DB2-6D48-447E-A1AC-900CDFB79266}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD2CB49-FC05-4D4C-A2AB-6463D42CCAD6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9540"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="heart" sheetId="1" r:id="rId1"/>
@@ -61,13 +61,13 @@
     <t>Thallium Stress Test Result</t>
   </si>
   <si>
-    <t>Predict</t>
+    <t>target</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -901,7 +901,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N290"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
